--- a/Data/Percent of replacement.xlsx
+++ b/Data/Percent of replacement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30516"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/55fd3f8ffa58db1a/Documents - Zircon Recrystallization/Manuscripts/MZ_Replacement/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="100" documentId="13_ncr:1_{244B0991-B060-4354-8AB6-4098CA8D143C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26563376-821A-4D91-ABDB-70AB89E20F89}"/>
+  <xr:revisionPtr revIDLastSave="101" documentId="13_ncr:1_{244B0991-B060-4354-8AB6-4098CA8D143C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72331906-4653-41E5-B1ED-E44A03593F1D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="percent of replacement" sheetId="1" r:id="rId1"/>
@@ -213,12 +213,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="0.00000"/>
-    <numFmt numFmtId="177" formatCode="0.0"/>
-    <numFmt numFmtId="178" formatCode="0.000"/>
-    <numFmt numFmtId="179" formatCode="0.0E+00"/>
+    <numFmt numFmtId="164" formatCode="0.00000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.0E+00"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -326,13 +326,13 @@
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -353,17 +353,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -381,7 +381,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -955,6 +955,24 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>2.1864581672554975</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>1.8700904168987775</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>1.6333200466507816</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>1.4494639856155267</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>1.3025668880079699</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.11881517660761903</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>1.0353671283329854E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1350,7 +1368,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3927,8 +3945,8 @@
       </cdr:nvGrpSpPr>
       <cdr:grpSpPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="2054210" y="603241"/>
-          <a:ext cx="2819387" cy="419097"/>
+          <a:off x="2055234" y="602544"/>
+          <a:ext cx="2820793" cy="418612"/>
           <a:chOff x="2054226" y="603250"/>
           <a:chExt cx="2819400" cy="419100"/>
         </a:xfrm>
@@ -4285,7 +4303,7 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">4454 0 24285,'-4454'513'0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">4233 0 24285,'-4233'530'0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -4313,7 +4331,7 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">2550 0 24274,'-2550'618'0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">2461 0 24274,'-2461'688'0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -4341,7 +4359,7 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 0 24442,'4182'759'0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 0 24442,'3943'794'0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -4397,7 +4415,7 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 25 24575,'0'-1'0,"0"0"0,1-1 0,-1 1 0,1 0 0,0 0 0,-1 0 0,1 1 0,0-1 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 1 0,1-1 0,-1 0 0,0 1 0,0-1 0,1 1 0,-1-1 0,0 1 0,0 0 0,1 0 0,-1 0 0,0 0 0,3 0 0,44-5 0,-42 5 0,466 0 0,-425 3 0,-1 1 0,0 3 0,1 1 0,53 17 0,171 66 0,-211-69 0,102 23 0,-23-8 0,260 110 0,-347-127 0,104 25 0,-93-30 0,60 25 0,-66-20 0,96 20 0,-40-13 0,159 63 0,-271-89 0,20 6-455,-2 1 0,26 14 0,-31-13-6371</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 27 24575,'0'-1'0,"0"0"0,1-1 0,-1 1 0,1 0 0,0 0 0,-1 0 0,1 1 0,0-2 0,0 1 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 1 0,0-1 0,1 1 0,-1-2 0,0 2 0,0 0 0,1 0 0,-1 0 0,0 0 0,3 0 0,42-5 0,-40 5 0,447 0 0,-407 3 0,-2 2 0,0 2 0,1 2 0,51 18 0,165 73 0,-204-76 0,99 26 0,-22-10 0,249 121 0,-333-139 0,100 27 0,-89-32 0,57 27 0,-63-23 0,92 23 0,-39-14 0,154 68 0,-261-96 0,19 5-455,-2 2 0,26 15 0,-31-14-6371</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -4425,7 +4443,7 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 0 24155,'159'565'0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 0 24155,'159'635'0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -4747,7 +4765,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O74"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.140625" style="1" bestFit="1" customWidth="1"/>
@@ -4763,7 +4781,7 @@
     <col min="13" max="13" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -4793,7 +4811,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15.6">
+    <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>9</v>
       </c>
@@ -4807,7 +4825,7 @@
       </c>
       <c r="F2" s="3"/>
     </row>
-    <row r="3" spans="1:15" ht="15.6">
+    <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
@@ -4821,7 +4839,7 @@
       </c>
       <c r="F3" s="3"/>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -4844,7 +4862,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15.6">
+    <row r="5" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>16</v>
       </c>
@@ -4892,7 +4910,7 @@
         <v>0.58394396087529044</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15.6">
+    <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
@@ -4940,7 +4958,7 @@
         <v>1.177436139097161</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15.6">
+    <row r="7" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>18</v>
       </c>
@@ -4988,7 +5006,7 @@
         <v>1.7709829789458644</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.6">
+    <row r="8" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>19</v>
       </c>
@@ -5045,7 +5063,7 @@
         <v>2.364584487973389</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.6">
+    <row r="9" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>20</v>
       </c>
@@ -5102,7 +5120,7 @@
         <v>2.9582406737331164</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.6">
+    <row r="10" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>21</v>
       </c>
@@ -5159,7 +5177,7 @@
         <v>3.5519515437798175</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.6">
+    <row r="11" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>22</v>
       </c>
@@ -5207,7 +5225,7 @@
         <v>4.1457171056696582</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.6">
+    <row r="12" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>23</v>
       </c>
@@ -5255,7 +5273,7 @@
         <v>4.7395373669601932</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15.6">
+    <row r="13" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>24</v>
       </c>
@@ -5312,7 +5330,7 @@
         <v>5.3334123352103688</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.6">
+    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>25</v>
       </c>
@@ -5360,7 +5378,7 @@
         <v>5.9273420179805303</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15.6">
+    <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>26</v>
       </c>
@@ -5408,7 +5426,7 @@
         <v>6.5213264228324119</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15.6">
+    <row r="16" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>27</v>
       </c>
@@ -5465,7 +5483,7 @@
         <v>7.1153655573291399</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15.6">
+    <row r="17" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>28</v>
       </c>
@@ -5513,7 +5531,7 @@
         <v>7.7094594290352374</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="15.6">
+    <row r="18" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>29</v>
       </c>
@@ -5570,7 +5588,7 @@
         <v>8.3036080455166204</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15.6">
+    <row r="19" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>30</v>
       </c>
@@ -5627,7 +5645,7 @@
         <v>8.8978114143405982</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15.6">
+    <row r="20" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
@@ -5648,7 +5666,7 @@
         <v>9.492069543075873</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="15.6">
+    <row r="21" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
@@ -5669,7 +5687,7 @@
         <v>10.086382439292557</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="15.6">
+    <row r="22" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="6"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
@@ -5690,7 +5708,7 @@
         <v>10.680750110562132</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="15.6">
+    <row r="23" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="6"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
@@ -5711,7 +5729,7 @@
         <v>11.275172564457499</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="15.6">
+    <row r="24" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>31</v>
       </c>
@@ -5768,7 +5786,7 @@
         <v>11.869649808552941</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="15.6">
+    <row r="25" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>32</v>
       </c>
@@ -5816,7 +5834,7 @@
         <v>4.0913068915052929E+19</v>
       </c>
       <c r="M25" s="3">
-        <f t="shared" ref="M25:M67" si="16">1000*183.31*L25/(6.022*10^23)</f>
+        <f t="shared" ref="M25:M73" si="16">1000*183.31*L25/(6.022*10^23)</f>
         <v>12.453959918330044</v>
       </c>
       <c r="N25" s="4">
@@ -5828,7 +5846,7 @@
         <v>12.464181850424142</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="15.6">
+    <row r="26" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>33</v>
       </c>
@@ -5885,7 +5903,7 @@
       </c>
       <c r="O26" s="3"/>
     </row>
-    <row r="27" spans="1:15">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>34</v>
       </c>
@@ -5930,7 +5948,7 @@
       </c>
       <c r="O27" s="3"/>
     </row>
-    <row r="28" spans="1:15">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K28">
         <v>1.25</v>
       </c>
@@ -5948,7 +5966,7 @@
       </c>
       <c r="O28" s="3"/>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K29">
         <v>1.3</v>
       </c>
@@ -5966,7 +5984,7 @@
       </c>
       <c r="O29" s="3"/>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K30">
         <v>1.35</v>
       </c>
@@ -5984,7 +6002,7 @@
       </c>
       <c r="O30" s="3"/>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K31">
         <v>1.4</v>
       </c>
@@ -6002,7 +6020,7 @@
       </c>
       <c r="O31" s="3"/>
     </row>
-    <row r="32" spans="1:15">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K32">
         <v>1.45</v>
       </c>
@@ -6020,7 +6038,7 @@
       </c>
       <c r="O32" s="3"/>
     </row>
-    <row r="33" spans="1:15">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>35</v>
       </c>
@@ -6065,7 +6083,7 @@
       </c>
       <c r="O33" s="3"/>
     </row>
-    <row r="34" spans="1:15">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>38</v>
       </c>
@@ -6118,7 +6136,7 @@
       </c>
       <c r="O34" s="3"/>
     </row>
-    <row r="35" spans="1:15">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>39</v>
       </c>
@@ -6171,7 +6189,7 @@
       </c>
       <c r="O35" s="3"/>
     </row>
-    <row r="36" spans="1:15">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>40</v>
       </c>
@@ -6224,7 +6242,7 @@
       </c>
       <c r="O36" s="3"/>
     </row>
-    <row r="37" spans="1:15">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>41</v>
       </c>
@@ -6277,7 +6295,7 @@
       </c>
       <c r="O37" s="3"/>
     </row>
-    <row r="38" spans="1:15">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>33</v>
       </c>
@@ -6325,13 +6343,13 @@
       </c>
       <c r="O38" s="3"/>
     </row>
-    <row r="39" spans="1:15">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="L39" s="4"/>
       <c r="M39" s="3"/>
       <c r="N39" s="4"/>
       <c r="O39" s="3"/>
     </row>
-    <row r="40" spans="1:15">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>42</v>
       </c>
@@ -6376,7 +6394,7 @@
       </c>
       <c r="O40" s="3"/>
     </row>
-    <row r="41" spans="1:15">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>35</v>
       </c>
@@ -6421,7 +6439,7 @@
       </c>
       <c r="O41" s="3"/>
     </row>
-    <row r="42" spans="1:15">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>38</v>
       </c>
@@ -6466,7 +6484,7 @@
       </c>
       <c r="O42" s="3"/>
     </row>
-    <row r="43" spans="1:15">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>39</v>
       </c>
@@ -6511,7 +6529,7 @@
       </c>
       <c r="O43" s="3"/>
     </row>
-    <row r="44" spans="1:15">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>41</v>
       </c>
@@ -6556,7 +6574,7 @@
       </c>
       <c r="O44" s="3"/>
     </row>
-    <row r="45" spans="1:15">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>33</v>
       </c>
@@ -6602,7 +6620,7 @@
       </c>
       <c r="O45" s="3"/>
     </row>
-    <row r="46" spans="1:15">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K46">
         <v>2.1</v>
       </c>
@@ -6620,7 +6638,7 @@
       </c>
       <c r="O46" s="3"/>
     </row>
-    <row r="47" spans="1:15">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K47">
         <v>2.15</v>
       </c>
@@ -6638,7 +6656,7 @@
       </c>
       <c r="O47" s="3"/>
     </row>
-    <row r="48" spans="1:15">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K48">
         <v>2.2000000000000002</v>
       </c>
@@ -6656,7 +6674,7 @@
       </c>
       <c r="O48" s="3"/>
     </row>
-    <row r="49" spans="11:15">
+    <row r="49" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K49">
         <v>2.25</v>
       </c>
@@ -6674,7 +6692,7 @@
       </c>
       <c r="O49" s="3"/>
     </row>
-    <row r="50" spans="11:15">
+    <row r="50" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K50">
         <v>2.2999999999999998</v>
       </c>
@@ -6692,7 +6710,7 @@
       </c>
       <c r="O50" s="3"/>
     </row>
-    <row r="51" spans="11:15">
+    <row r="51" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K51">
         <v>2.35</v>
       </c>
@@ -6710,7 +6728,7 @@
       </c>
       <c r="O51" s="3"/>
     </row>
-    <row r="52" spans="11:15">
+    <row r="52" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K52">
         <v>2.4</v>
       </c>
@@ -6728,7 +6746,7 @@
       </c>
       <c r="O52" s="3"/>
     </row>
-    <row r="53" spans="11:15">
+    <row r="53" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K53">
         <v>2.4500000000000002</v>
       </c>
@@ -6746,7 +6764,7 @@
       </c>
       <c r="O53" s="3"/>
     </row>
-    <row r="54" spans="11:15">
+    <row r="54" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K54">
         <v>2.5</v>
       </c>
@@ -6764,7 +6782,7 @@
       </c>
       <c r="O54" s="3"/>
     </row>
-    <row r="55" spans="11:15">
+    <row r="55" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K55">
         <v>2.5499999999999998</v>
       </c>
@@ -6782,7 +6800,7 @@
       </c>
       <c r="O55" s="3"/>
     </row>
-    <row r="56" spans="11:15">
+    <row r="56" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K56">
         <v>2.6</v>
       </c>
@@ -6800,7 +6818,7 @@
       </c>
       <c r="O56" s="3"/>
     </row>
-    <row r="57" spans="11:15">
+    <row r="57" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K57">
         <v>2.65</v>
       </c>
@@ -6818,7 +6836,7 @@
       </c>
       <c r="O57" s="3"/>
     </row>
-    <row r="58" spans="11:15">
+    <row r="58" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K58">
         <v>2.7</v>
       </c>
@@ -6836,7 +6854,7 @@
       </c>
       <c r="O58" s="3"/>
     </row>
-    <row r="59" spans="11:15">
+    <row r="59" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K59">
         <v>2.75</v>
       </c>
@@ -6854,7 +6872,7 @@
       </c>
       <c r="O59" s="3"/>
     </row>
-    <row r="60" spans="11:15">
+    <row r="60" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K60">
         <v>2.8</v>
       </c>
@@ -6872,7 +6890,7 @@
       </c>
       <c r="O60" s="3"/>
     </row>
-    <row r="61" spans="11:15">
+    <row r="61" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K61">
         <v>2.85</v>
       </c>
@@ -6890,7 +6908,7 @@
       </c>
       <c r="O61" s="3"/>
     </row>
-    <row r="62" spans="11:15">
+    <row r="62" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K62">
         <v>2.9</v>
       </c>
@@ -6908,7 +6926,7 @@
       </c>
       <c r="O62" s="3"/>
     </row>
-    <row r="63" spans="11:15">
+    <row r="63" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K63">
         <v>2.95</v>
       </c>
@@ -6926,7 +6944,7 @@
       </c>
       <c r="O63" s="3"/>
     </row>
-    <row r="64" spans="11:15">
+    <row r="64" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K64">
         <v>3</v>
       </c>
@@ -6944,7 +6962,7 @@
       </c>
       <c r="O64" s="3"/>
     </row>
-    <row r="65" spans="11:15">
+    <row r="65" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K65">
         <v>4</v>
       </c>
@@ -6962,7 +6980,7 @@
       </c>
       <c r="O65" s="3"/>
     </row>
-    <row r="66" spans="11:15">
+    <row r="66" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K66">
         <v>5</v>
       </c>
@@ -6980,7 +6998,7 @@
       </c>
       <c r="O66" s="3"/>
     </row>
-    <row r="67" spans="11:15">
+    <row r="67" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K67">
         <v>6</v>
       </c>
@@ -6998,7 +7016,7 @@
       </c>
       <c r="O67" s="3"/>
     </row>
-    <row r="68" spans="11:15">
+    <row r="68" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K68">
         <v>7</v>
       </c>
@@ -7006,14 +7024,17 @@
         <f t="shared" si="1"/>
         <v>6.1435188972584346E+18</v>
       </c>
-      <c r="M68" s="3"/>
+      <c r="M68" s="3">
+        <f t="shared" si="16"/>
+        <v>1.8700904168987775</v>
+      </c>
       <c r="N68" s="4">
         <f t="shared" si="2"/>
         <v>2.7268624362121249E+20</v>
       </c>
       <c r="O68" s="3"/>
     </row>
-    <row r="69" spans="11:15">
+    <row r="69" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K69">
         <v>8</v>
       </c>
@@ -7021,14 +7042,17 @@
         <f t="shared" si="1"/>
         <v>5.3656938088107612E+18</v>
       </c>
-      <c r="M69" s="3"/>
+      <c r="M69" s="3">
+        <f t="shared" si="16"/>
+        <v>1.6333200466507816</v>
+      </c>
       <c r="N69" s="4">
         <f t="shared" si="2"/>
         <v>3.1221555877051335E+20</v>
       </c>
       <c r="O69" s="3"/>
     </row>
-    <row r="70" spans="11:15">
+    <row r="70" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K70">
         <v>9</v>
       </c>
@@ -7036,14 +7060,17 @@
         <f t="shared" si="1"/>
         <v>4.7616999189224274E+18</v>
       </c>
-      <c r="M70" s="3"/>
+      <c r="M70" s="3">
+        <f t="shared" si="16"/>
+        <v>1.4494639856155267</v>
+      </c>
       <c r="N70" s="4">
         <f t="shared" si="2"/>
         <v>3.5181828322529942E+20</v>
       </c>
       <c r="O70" s="3"/>
     </row>
-    <row r="71" spans="11:15">
+    <row r="71" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K71">
         <v>10</v>
       </c>
@@ -7051,14 +7078,17 @@
         <f t="shared" ref="L71:L73" si="26">($E$9*$E$8*($E$11-$K71*$E$12))/($E$10*($K71*$E$19-$E$18))</f>
         <v>4.2791215970672604E+18</v>
       </c>
-      <c r="M71" s="3"/>
+      <c r="M71" s="3">
+        <f t="shared" si="16"/>
+        <v>1.3025668880079699</v>
+      </c>
       <c r="N71" s="4">
         <f t="shared" ref="N71:N73" si="27">($E$9*$E$8*($E$18-$K71*$E$19))/($E$10*($K71*$E$12-$E$11))</f>
         <v>3.9149462166662611E+20</v>
       </c>
       <c r="O71" s="3"/>
     </row>
-    <row r="72" spans="11:15">
+    <row r="72" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K72">
         <v>100</v>
       </c>
@@ -7066,14 +7096,17 @@
         <f t="shared" si="26"/>
         <v>3.9032512876061414E+17</v>
       </c>
-      <c r="M72" s="3"/>
+      <c r="M72" s="3">
+        <f t="shared" si="16"/>
+        <v>0.11881517660761903</v>
+      </c>
       <c r="N72" s="4">
         <f t="shared" si="27"/>
         <v>4.2919427094758388E+21</v>
       </c>
       <c r="O72" s="3"/>
     </row>
-    <row r="73" spans="11:15">
+    <row r="73" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K73">
         <v>1000</v>
       </c>
@@ -7081,14 +7114,17 @@
         <f t="shared" si="26"/>
         <v>3401331540462189</v>
       </c>
-      <c r="M73" s="3"/>
+      <c r="M73" s="3">
+        <f t="shared" si="16"/>
+        <v>1.0353671283329854E-3</v>
+      </c>
       <c r="N73" s="4">
         <f t="shared" si="27"/>
         <v>4.9252860851126987E+23</v>
       </c>
       <c r="O73" s="3"/>
     </row>
-    <row r="74" spans="11:15">
+    <row r="74" spans="11:15" x14ac:dyDescent="0.25">
       <c r="L74" s="4"/>
       <c r="M74" s="3"/>
     </row>
@@ -7103,14 +7139,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FAF1012-BC51-44C7-9420-2DDDC23FE7AD}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" thickBot="1">
+    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11"/>
       <c r="B1" s="12" t="s">
         <v>1</v>
@@ -7122,7 +7158,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" thickBot="1">
+    <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>46</v>
       </c>
@@ -7136,7 +7172,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" thickBot="1">
+    <row r="3" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
         <v>47</v>
       </c>
@@ -7150,7 +7186,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" thickBot="1">
+    <row r="4" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
         <v>17</v>
       </c>
@@ -7164,7 +7200,7 @@
         <v>17544.09</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" thickBot="1">
+    <row r="5" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
         <v>48</v>
       </c>
@@ -7178,7 +7214,7 @@
         <v>19.25</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" thickBot="1">
+    <row r="6" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
         <v>49</v>
       </c>
@@ -7192,7 +7228,7 @@
         <v>15195.9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" thickBot="1">
+    <row r="7" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
         <v>50</v>
       </c>
@@ -7206,7 +7242,7 @@
         <v>19.920000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" thickBot="1">
+    <row r="8" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>51</v>
       </c>
@@ -7220,7 +7256,7 @@
         <v>65715</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" thickBot="1">
+    <row r="9" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>52</v>
       </c>
@@ -7234,7 +7270,7 @@
         <v>355756</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15" thickBot="1">
+    <row r="10" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
         <v>53</v>
       </c>
@@ -7257,7 +7293,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29F147B5-4DC4-4651-81D5-387BC5EEA40C}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7268,7 +7304,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13ED1FC9-CEE1-4BFD-9CD2-0AD2E0B3A2CD}">
   <dimension ref="A1:O74"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.140625" style="1" bestFit="1" customWidth="1"/>
@@ -7284,7 +7320,7 @@
     <col min="13" max="13" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -7314,7 +7350,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15.6">
+    <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>9</v>
       </c>
@@ -7328,7 +7364,7 @@
       </c>
       <c r="F2" s="3"/>
     </row>
-    <row r="3" spans="1:15" ht="15.6">
+    <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
@@ -7342,7 +7378,7 @@
       </c>
       <c r="F3" s="3"/>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -7365,7 +7401,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15.6">
+    <row r="5" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>16</v>
       </c>
@@ -7413,7 +7449,7 @@
         <v>0.29197198043764522</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15.6">
+    <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
@@ -7461,7 +7497,7 @@
         <v>0.58871806954858052</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15.6">
+    <row r="7" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>18</v>
       </c>
@@ -7509,7 +7545,7 @@
         <v>0.88549148947293221</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.6">
+    <row r="8" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>19</v>
       </c>
@@ -7566,7 +7602,7 @@
         <v>1.1822922439866945</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.6">
+    <row r="9" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>20</v>
       </c>
@@ -7614,7 +7650,7 @@
         <v>1.4791203368665582</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.6">
+    <row r="10" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>21</v>
       </c>
@@ -7662,7 +7698,7 @@
         <v>1.7759757718899087</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.6">
+    <row r="11" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>22</v>
       </c>
@@ -7710,7 +7746,7 @@
         <v>2.0728585528348291</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.6">
+    <row r="12" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>23</v>
       </c>
@@ -7758,7 +7794,7 @@
         <v>2.3697686834800966</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15.6">
+    <row r="13" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>24</v>
       </c>
@@ -7815,7 +7851,7 @@
         <v>2.6667061676051844</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.6">
+    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>25</v>
       </c>
@@ -7863,7 +7899,7 @@
         <v>2.9636710089902651</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15.6">
+    <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>26</v>
       </c>
@@ -7911,7 +7947,7 @@
         <v>3.260663211416206</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15.6">
+    <row r="16" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>27</v>
       </c>
@@ -7968,7 +8004,7 @@
         <v>3.5576827786645695</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15.6">
+    <row r="17" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>28</v>
       </c>
@@ -8016,7 +8052,7 @@
         <v>3.8547297145176178</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="15.6">
+    <row r="18" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>29</v>
       </c>
@@ -8073,7 +8109,7 @@
         <v>4.1518040227583102</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15.6">
+    <row r="19" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>30</v>
       </c>
@@ -8130,7 +8166,7 @@
         <v>4.4489057071702991</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15.6">
+    <row r="20" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
@@ -8151,7 +8187,7 @@
         <v>4.7460347715379374</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="15.6">
+    <row r="21" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
@@ -8172,7 +8208,7 @@
         <v>5.0431912196462783</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="15.6">
+    <row r="22" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="6"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
@@ -8193,7 +8229,7 @@
         <v>5.3403750552810658</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="15.6">
+    <row r="23" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="6"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
@@ -8214,7 +8250,7 @@
         <v>5.6375862822287495</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="15.6">
+    <row r="24" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>31</v>
       </c>
@@ -8271,7 +8307,7 @@
         <v>5.9348249042764705</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="15.6">
+    <row r="25" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>32</v>
       </c>
@@ -8331,7 +8367,7 @@
         <v>6.23209092521207</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="15.6">
+    <row r="26" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>33</v>
       </c>
@@ -8388,7 +8424,7 @@
       </c>
       <c r="O26" s="3"/>
     </row>
-    <row r="27" spans="1:15">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>34</v>
       </c>
@@ -8433,7 +8469,7 @@
       </c>
       <c r="O27" s="3"/>
     </row>
-    <row r="28" spans="1:15">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K28">
         <v>1.25</v>
       </c>
@@ -8451,7 +8487,7 @@
       </c>
       <c r="O28" s="3"/>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K29">
         <v>1.3</v>
       </c>
@@ -8469,7 +8505,7 @@
       </c>
       <c r="O29" s="3"/>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K30">
         <v>1.35</v>
       </c>
@@ -8487,7 +8523,7 @@
       </c>
       <c r="O30" s="3"/>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K31">
         <v>1.4</v>
       </c>
@@ -8505,7 +8541,7 @@
       </c>
       <c r="O31" s="3"/>
     </row>
-    <row r="32" spans="1:15">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K32">
         <v>1.45</v>
       </c>
@@ -8523,7 +8559,7 @@
       </c>
       <c r="O32" s="3"/>
     </row>
-    <row r="33" spans="2:15">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -8545,7 +8581,7 @@
       </c>
       <c r="O33" s="3"/>
     </row>
-    <row r="34" spans="2:15">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -8567,7 +8603,7 @@
       </c>
       <c r="O34" s="3"/>
     </row>
-    <row r="35" spans="2:15">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C35" s="17"/>
       <c r="D35" s="17"/>
       <c r="E35" s="17"/>
@@ -8593,7 +8629,7 @@
       </c>
       <c r="O35" s="3"/>
     </row>
-    <row r="36" spans="2:15">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -8615,7 +8651,7 @@
       </c>
       <c r="O36" s="3"/>
     </row>
-    <row r="37" spans="2:15">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C37" s="17"/>
       <c r="D37" s="17"/>
       <c r="E37" s="17"/>
@@ -8641,7 +8677,7 @@
       </c>
       <c r="O37" s="3"/>
     </row>
-    <row r="38" spans="2:15">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
       <c r="K38">
         <v>1.75</v>
       </c>
@@ -8659,13 +8695,13 @@
       </c>
       <c r="O38" s="3"/>
     </row>
-    <row r="39" spans="2:15">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
       <c r="L39" s="4"/>
       <c r="M39" s="3"/>
       <c r="N39" s="4"/>
       <c r="O39" s="3"/>
     </row>
-    <row r="40" spans="2:15">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -8687,7 +8723,7 @@
       </c>
       <c r="O40" s="3"/>
     </row>
-    <row r="41" spans="2:15">
+    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F41"/>
       <c r="G41" s="1"/>
       <c r="K41">
@@ -8707,7 +8743,7 @@
       </c>
       <c r="O41" s="3"/>
     </row>
-    <row r="42" spans="2:15">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F42"/>
       <c r="G42" s="1"/>
       <c r="K42">
@@ -8727,7 +8763,7 @@
       </c>
       <c r="O42" s="3"/>
     </row>
-    <row r="43" spans="2:15">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C43" s="18"/>
       <c r="D43" s="18"/>
       <c r="E43" s="18"/>
@@ -8753,7 +8789,7 @@
       </c>
       <c r="O43" s="3"/>
     </row>
-    <row r="44" spans="2:15">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C44" s="18"/>
       <c r="D44" s="18"/>
       <c r="E44" s="18"/>
@@ -8779,7 +8815,7 @@
       </c>
       <c r="O44" s="3"/>
     </row>
-    <row r="45" spans="2:15">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B45" s="20"/>
       <c r="C45" s="20"/>
       <c r="D45" s="20"/>
@@ -8806,7 +8842,7 @@
       </c>
       <c r="O45" s="3"/>
     </row>
-    <row r="46" spans="2:15">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
       <c r="K46">
         <v>2.1</v>
       </c>
@@ -8824,7 +8860,7 @@
       </c>
       <c r="O46" s="3"/>
     </row>
-    <row r="47" spans="2:15">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
       <c r="K47">
         <v>2.15</v>
       </c>
@@ -8842,7 +8878,7 @@
       </c>
       <c r="O47" s="3"/>
     </row>
-    <row r="48" spans="2:15">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
       <c r="K48">
         <v>2.2000000000000002</v>
       </c>
@@ -8860,7 +8896,7 @@
       </c>
       <c r="O48" s="3"/>
     </row>
-    <row r="49" spans="11:15">
+    <row r="49" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K49">
         <v>2.25</v>
       </c>
@@ -8878,7 +8914,7 @@
       </c>
       <c r="O49" s="3"/>
     </row>
-    <row r="50" spans="11:15">
+    <row r="50" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K50">
         <v>2.2999999999999998</v>
       </c>
@@ -8896,7 +8932,7 @@
       </c>
       <c r="O50" s="3"/>
     </row>
-    <row r="51" spans="11:15">
+    <row r="51" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K51">
         <v>2.35</v>
       </c>
@@ -8914,7 +8950,7 @@
       </c>
       <c r="O51" s="3"/>
     </row>
-    <row r="52" spans="11:15">
+    <row r="52" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K52">
         <v>2.4</v>
       </c>
@@ -8932,7 +8968,7 @@
       </c>
       <c r="O52" s="3"/>
     </row>
-    <row r="53" spans="11:15">
+    <row r="53" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K53">
         <v>2.4500000000000002</v>
       </c>
@@ -8950,7 +8986,7 @@
       </c>
       <c r="O53" s="3"/>
     </row>
-    <row r="54" spans="11:15">
+    <row r="54" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K54">
         <v>2.5</v>
       </c>
@@ -8968,7 +9004,7 @@
       </c>
       <c r="O54" s="3"/>
     </row>
-    <row r="55" spans="11:15">
+    <row r="55" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K55">
         <v>2.5499999999999998</v>
       </c>
@@ -8986,7 +9022,7 @@
       </c>
       <c r="O55" s="3"/>
     </row>
-    <row r="56" spans="11:15">
+    <row r="56" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K56">
         <v>2.6</v>
       </c>
@@ -9004,7 +9040,7 @@
       </c>
       <c r="O56" s="3"/>
     </row>
-    <row r="57" spans="11:15">
+    <row r="57" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K57">
         <v>2.65</v>
       </c>
@@ -9022,7 +9058,7 @@
       </c>
       <c r="O57" s="3"/>
     </row>
-    <row r="58" spans="11:15">
+    <row r="58" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K58">
         <v>2.7</v>
       </c>
@@ -9040,7 +9076,7 @@
       </c>
       <c r="O58" s="3"/>
     </row>
-    <row r="59" spans="11:15">
+    <row r="59" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K59">
         <v>2.75</v>
       </c>
@@ -9058,7 +9094,7 @@
       </c>
       <c r="O59" s="3"/>
     </row>
-    <row r="60" spans="11:15">
+    <row r="60" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K60">
         <v>2.8</v>
       </c>
@@ -9076,7 +9112,7 @@
       </c>
       <c r="O60" s="3"/>
     </row>
-    <row r="61" spans="11:15">
+    <row r="61" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K61">
         <v>2.85</v>
       </c>
@@ -9094,7 +9130,7 @@
       </c>
       <c r="O61" s="3"/>
     </row>
-    <row r="62" spans="11:15">
+    <row r="62" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K62">
         <v>2.9</v>
       </c>
@@ -9112,7 +9148,7 @@
       </c>
       <c r="O62" s="3"/>
     </row>
-    <row r="63" spans="11:15">
+    <row r="63" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K63">
         <v>2.95</v>
       </c>
@@ -9130,7 +9166,7 @@
       </c>
       <c r="O63" s="3"/>
     </row>
-    <row r="64" spans="11:15">
+    <row r="64" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K64">
         <v>3</v>
       </c>
@@ -9148,7 +9184,7 @@
       </c>
       <c r="O64" s="3"/>
     </row>
-    <row r="65" spans="11:15">
+    <row r="65" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K65">
         <v>4</v>
       </c>
@@ -9166,7 +9202,7 @@
       </c>
       <c r="O65" s="3"/>
     </row>
-    <row r="66" spans="11:15">
+    <row r="66" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K66">
         <v>5</v>
       </c>
@@ -9184,7 +9220,7 @@
       </c>
       <c r="O66" s="3"/>
     </row>
-    <row r="67" spans="11:15">
+    <row r="67" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K67">
         <v>6</v>
       </c>
@@ -9202,7 +9238,7 @@
       </c>
       <c r="O67" s="3"/>
     </row>
-    <row r="68" spans="11:15">
+    <row r="68" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K68">
         <v>7</v>
       </c>
@@ -9217,7 +9253,7 @@
       </c>
       <c r="O68" s="3"/>
     </row>
-    <row r="69" spans="11:15">
+    <row r="69" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K69">
         <v>8</v>
       </c>
@@ -9232,7 +9268,7 @@
       </c>
       <c r="O69" s="3"/>
     </row>
-    <row r="70" spans="11:15">
+    <row r="70" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K70">
         <v>9</v>
       </c>
@@ -9247,7 +9283,7 @@
       </c>
       <c r="O70" s="3"/>
     </row>
-    <row r="71" spans="11:15">
+    <row r="71" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K71">
         <v>10</v>
       </c>
@@ -9262,7 +9298,7 @@
       </c>
       <c r="O71" s="3"/>
     </row>
-    <row r="72" spans="11:15">
+    <row r="72" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K72">
         <v>100</v>
       </c>
@@ -9277,7 +9313,7 @@
       </c>
       <c r="O72" s="3"/>
     </row>
-    <row r="73" spans="11:15">
+    <row r="73" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K73">
         <v>1000</v>
       </c>
@@ -9292,7 +9328,7 @@
       </c>
       <c r="O73" s="3"/>
     </row>
-    <row r="74" spans="11:15">
+    <row r="74" spans="11:15" x14ac:dyDescent="0.25">
       <c r="L74" s="4"/>
       <c r="M74" s="3"/>
     </row>
@@ -9304,15 +9340,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="734d9d5b-bad1-43ae-a310-979dd75c40ab">
@@ -9323,7 +9350,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004E97729A3E6EAA4F9E1C9F13D541663D" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c051356ea1710f3fb5d80eaeb75cb6ec">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="734d9d5b-bad1-43ae-a310-979dd75c40ab" xmlns:ns3="ad78e214-34d5-4fdd-b75d-5961e8c71fd9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1b8103a8cf90e9c87e2e092ffa6eae69" ns2:_="" ns3:_="">
     <xsd:import namespace="734d9d5b-bad1-43ae-a310-979dd75c40ab"/>
@@ -9552,14 +9579,49 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C49C172C-0B1C-412F-8657-D9CFB90D8B09}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF509A77-8F89-478B-B78A-02F8FB02C95D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="734d9d5b-bad1-43ae-a310-979dd75c40ab"/>
+    <ds:schemaRef ds:uri="ad78e214-34d5-4fdd-b75d-5961e8c71fd9"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF509A77-8F89-478B-B78A-02F8FB02C95D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50E85A1D-74A2-4BE3-97D9-38C4D0641CB9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="734d9d5b-bad1-43ae-a310-979dd75c40ab"/>
+    <ds:schemaRef ds:uri="ad78e214-34d5-4fdd-b75d-5961e8c71fd9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50E85A1D-74A2-4BE3-97D9-38C4D0641CB9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C49C172C-0B1C-412F-8657-D9CFB90D8B09}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>